--- a/backend/data/financials_by_company/1400.HK.xlsx
+++ b/backend/data/financials_by_company/1400.HK.xlsx
@@ -4066,7 +4066,7 @@
         <v>-11716000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
         <v>0.0010000002</v>
